--- a/исходник.xlsx
+++ b/исходник.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tsvetkovds\Documents\.PROJECTS\anastasiya\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7593FCFF-7901-42BD-B73A-22C0956DC49C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D68101DF-23C0-407C-A9CC-EBF904178108}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="151">
   <si>
     <t>№</t>
   </si>
@@ -478,6 +478,9 @@
   </si>
   <si>
     <t>Таблица считывается с 13 строки, то что выше не имеет значения</t>
+  </si>
+  <si>
+    <t>999</t>
   </si>
 </sst>
 </file>
@@ -986,7 +989,7 @@
         <v>35</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>48</v>
+        <v>150</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>49</v>
